--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-practitioner.xlsx
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -649,7 +649,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Practitioner.telecom.system</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2857" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2865" uniqueCount="517">
   <si>
     <t>Property</t>
   </si>
@@ -368,7 +368,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1333,7 +1333,7 @@
     <t>Practitioner.qualification.issuer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1379,12 +1379,6 @@
     <t>都道府県別 麻薬施用者免許番号</t>
   </si>
   <si>
-    <t>この役割におけるこの人の資格に適用されるidentifier。 / An identifier that applies to this person's qualification in this role.</t>
-  </si>
-  <si>
-    <t>多くの場合、資格に特定のIDが割り当てられます。 / Often, specific identities are assigned for the qualification.</t>
-  </si>
-  <si>
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.identifier.id</t>
   </si>
   <si>
@@ -1451,7 +1445,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1617,9 +1611,6 @@
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.code</t>
   </si>
   <si>
-    <t>資格のコード化された表現。 / Coded representation of the qualification.</t>
-  </si>
-  <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_MedicalLicenseCertificate_CS"/&gt;
@@ -1634,16 +1625,7 @@
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.period</t>
   </si>
   <si>
-    <t>資格が有効な期間。 / Period during which the qualification is valid.</t>
-  </si>
-  <si>
-    <t>資格は多くの場合、限られた期間であり、取り消すことができます。 / Qualifications are often for a limited period of time, and can be revoked.</t>
-  </si>
-  <si>
     <t>Practitioner.qualification:narcoticPrescriptionLicenseNumber.issuer</t>
-  </si>
-  <si>
-    <t>資格を規制および発行する組織。 / Organization that regulates and issues the qualification.</t>
   </si>
   <si>
     <t>Practitioner.qualification:medicalRegistrationNumber</t>
@@ -2048,17 +2030,17 @@
   <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="75.0546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.8671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="33.61328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="64.34765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.89453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="28.8203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.1796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="60.1640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2067,26 +2049,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.75390625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.0859375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="107.3984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="52.3828125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="92.07421875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="44.90625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7737,11 +7719,13 @@
         <v>420</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7819,10 +7803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7931,10 +7915,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8045,10 +8029,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8074,16 +8058,16 @@
         <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8111,28 +8095,28 @@
         <v>202</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8150,7 +8134,7 @@
         <v>132</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8161,10 +8145,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8190,16 +8174,16 @@
         <v>390</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8224,31 +8208,31 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="Y54" t="s" s="2">
+      <c r="AA54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8263,10 +8247,10 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8277,10 +8261,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8306,16 +8290,16 @@
         <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8364,7 +8348,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8379,13 +8363,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8393,10 +8377,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8422,13 +8406,13 @@
         <v>184</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8478,7 +8462,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8493,10 +8477,10 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>219</v>
@@ -8507,10 +8491,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8536,10 +8520,10 @@
         <v>238</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8590,7 +8574,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8605,10 +8589,10 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>244</v>
@@ -8619,10 +8603,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8645,16 +8629,16 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8704,7 +8688,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8719,13 +8703,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8733,7 +8717,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>389</v>
@@ -8765,9 +8749,11 @@
         <v>391</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8777,7 +8763,7 @@
         <v>78</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>78</v>
@@ -8796,7 +8782,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -8843,7 +8829,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>398</v>
@@ -8875,11 +8861,13 @@
         <v>399</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>489</v>
+        <v>402</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8957,7 +8945,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>405</v>
@@ -8983,15 +8971,17 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>407</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9069,13 +9059,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>367</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>78</v>
@@ -9183,7 +9173,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>376</v>
@@ -9295,7 +9285,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>377</v>
@@ -9409,7 +9399,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>378</v>
@@ -9525,7 +9515,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>383</v>
@@ -9554,14 +9544,16 @@
         <v>147</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>422</v>
+        <v>387</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9639,10 +9631,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9751,10 +9743,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9865,10 +9857,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9894,16 +9886,16 @@
         <v>109</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -9931,28 +9923,28 @@
         <v>202</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9970,7 +9962,7 @@
         <v>132</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9981,10 +9973,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10010,16 +10002,16 @@
         <v>390</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10044,31 +10036,31 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="Y70" t="s" s="2">
+      <c r="AA70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10083,10 +10075,10 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10097,10 +10089,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10126,23 +10118,23 @@
         <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>78</v>
@@ -10184,7 +10176,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10199,13 +10191,13 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10213,10 +10205,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10242,13 +10234,13 @@
         <v>184</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10298,7 +10290,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10313,10 +10305,10 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>219</v>
@@ -10327,10 +10319,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10356,10 +10348,10 @@
         <v>238</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10410,7 +10402,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10425,10 +10417,10 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>244</v>
@@ -10439,10 +10431,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10465,16 +10457,16 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10524,7 +10516,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10539,13 +10531,13 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10553,7 +10545,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>389</v>
@@ -10585,9 +10577,11 @@
         <v>391</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10597,7 +10591,7 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>78</v>
@@ -10616,7 +10610,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10663,7 +10657,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>398</v>
@@ -10695,11 +10689,13 @@
         <v>399</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="O76" t="s" s="2">
-        <v>489</v>
+        <v>402</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10777,7 +10773,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>405</v>
@@ -10803,15 +10799,17 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>407</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -10889,10 +10887,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10918,16 +10916,16 @@
         <v>390</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -10976,7 +10974,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10991,13 +10989,13 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-practitioner.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
